--- a/marketing_forms/012_customer_acquisition_strategy_feedback_form--marketing_forms.xlsx
+++ b/marketing_forms/012_customer_acquisition_strategy_feedback_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What do you think of this form?</t>
+          <t>How do you feel about the current customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What would you like to improve?</t>
+          <t>What changes would you suggest we make to improve the strategy?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Would you like to be contacted?</t>
+          <t>Would you like to be contacted for further feedback or updates?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What can we improve?</t>
+          <t>How can we better support you with your current needs?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How can we improve?</t>
+          <t>What features would you like to see in future updates to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What would you like to change?</t>
+          <t>Can we contact you for feedback or updates in the future?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you feel?</t>
+          <t>How likely are you to recommend our company to others based on the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Can we contact you?</t>
+          <t>Are there any features or services offered by our competitors that you would like to see us offer?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How can we help you?</t>
+          <t>Can we help you with anything else related to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Do you have any feedback?</t>
+          <t>How can we improve the current form design to make it more user-friendly?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Can we send you updates?</t>
+          <t>Would you like to see any additional information or features added to the form in the future?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Would you like to be contacted?</t>
+          <t>Can we contact you to discuss your feedback or questions about the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Is the form helpful?</t>
+          <t>Can we contact you for further feedback or updates?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is missing?</t>
+          <t>How can we help you with anything else related to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Can we help you with anything else?</t>
+          <t>What do you like to see in the future related to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Can we send you updates?</t>
+          <t>Can we contact you for updates related to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What do you like about the form?</t>
+          <t>Is there anything else you would like to mention about the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,174 +916,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Can we contact you?</t>
+          <t>Can we send you updates related to the customer acquisition strategy?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What do you dislike about the form?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Can we send you updates?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How can we help you?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Can we help you with anything else?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What do you like to see?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Can we contact you?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What do you like to see in the future?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,357 +965,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_3_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_true}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': True}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_3_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_false}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': False}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_7_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'positive'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Positive'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_7_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'negative'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'Negative'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_7_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'neutral'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'Neutral'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_8_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_8_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_11_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_12_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_11_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_12_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_90,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 90, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_12_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_13_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_100,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 100, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_12_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_13_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_110,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 110, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_13_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_16_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_120,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 120, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_13_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_16_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_130,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 130, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_16_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_18_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_140,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 140, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_acquisition_strategy_feedback_form_16_choices</t>
+          <t>customer_acquisition_strategy_feedback_form_18_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_150,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 150, 'name': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_18_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_160,_'name':_true}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 160, 'name': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_18_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_170,_'name':_false}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 170, 'name': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_180,_'name':_true}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 180, 'name': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_190,_'name':_false}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 190, 'name': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_200,_'name':_true}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 200, 'name': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>customer_acquisition_strategy_feedback_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_210,_'name':_false}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 210, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
